--- a/packages-generated/GB Accounts Self Employed 2024-04-05 (Apr24) Excel 2007/Vat.xlsx
+++ b/packages-generated/GB Accounts Self Employed 2024-04-05 (Apr24) Excel 2007/Vat.xlsx
@@ -40,7 +40,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="3">VATQtr4!$A$1:$I$32</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">VATQtr5!$A$1:$I$32</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="F5" s="144"/>
       <c r="G5" s="42">
-        <v>45838</v>
+        <v>45138</v>
       </c>
       <c r="H5" s="10"/>
       <c r="I5" s="13"/>
@@ -13968,7 +13968,7 @@
       </c>
       <c r="F5" s="144"/>
       <c r="G5" s="42">
-        <v>45930</v>
+        <v>45230</v>
       </c>
       <c r="H5" s="10"/>
       <c r="I5" s="13"/>
@@ -14514,7 +14514,7 @@
       </c>
       <c r="F5" s="144"/>
       <c r="G5" s="42">
-        <v>46022</v>
+        <v>45322</v>
       </c>
       <c r="H5" s="10"/>
       <c r="I5" s="13"/>
@@ -15060,7 +15060,7 @@
       </c>
       <c r="F5" s="144"/>
       <c r="G5" s="42">
-        <v>46112</v>
+        <v>45412</v>
       </c>
       <c r="H5" s="10"/>
       <c r="I5" s="13"/>
@@ -15606,7 +15606,7 @@
       </c>
       <c r="F5" s="144"/>
       <c r="G5" s="42">
-        <v>46142</v>
+        <v>45443</v>
       </c>
       <c r="H5" s="10"/>
       <c r="I5" s="13"/>
